--- a/Психологический_центр_готово/01_Лабораторная_1_Сетевое_анкетирование/Лабораторная1_Ответы_собственной_анкеты.xlsx
+++ b/Психологический_центр_готово/01_Лабораторная_1_Сетевое_анкетирование/Лабораторная1_Ответы_собственной_анкеты.xlsx
@@ -438,7 +438,7 @@
   <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="95" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/Психологический_центр_готово/01_Лабораторная_1_Сетевое_анкетирование/Лабораторная1_Ответы_собственной_анкеты.xlsx
+++ b/Психологический_центр_готово/01_Лабораторная_1_Сетевое_анкетирование/Лабораторная1_Ответы_собственной_анкеты.xlsx
@@ -8,8 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ссылка" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ответы" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Структура анкеты" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ответы Google Forms" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Структура анкеты" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,8 +19,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="3">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="m/d/yyyy h:mm:ss"/>
+  </numFmts>
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,11 +32,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
+      <color theme="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <b val="1"/>
       <sz val="10"/>
     </font>
@@ -46,11 +55,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DDEDEA"/>
+        <fgColor rgb="00DCEAF7"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -58,17 +67,35 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border/>
+    <border>
+      <left style="thin">
+        <color rgb="008A8F98"/>
+      </left>
+      <right style="thin">
+        <color rgb="008A8F98"/>
+      </right>
+      <top style="thin">
+        <color rgb="008A8F98"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="008A8F98"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -438,18 +465,18 @@
   <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="100" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Адрес Google Forms</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>https://docs.google.com/forms/d/e/1FAIpQLSe0oX0oEvjGYzM3l64gNccCgbLFiAm_FGf6AoDJIpr168NVzg/viewform</t>
         </is>
@@ -466,244 +493,316 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="42" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="37" customWidth="1" min="9" max="9"/>
+    <col width="42" customWidth="1" min="10" max="10"/>
+    <col width="42" customWidth="1" min="11" max="11"/>
+    <col width="42" customWidth="1" min="12" max="12"/>
+    <col width="42" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Отметка времени</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>Возраст</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Пол</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Как часто вы испытываете эмоциональное напряжение в течение недели?</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Какие ситуации чаще всего вызывают у вас стресс?</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Оцените уровень психологического комфорта за последнюю неделю</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Насколько легко вам обращаться за помощью?</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Что помогает вам восстановиться после напряженного дня?</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Есть ли у вас стабильный режим сна?</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Сколько часов в среднем вы спите в сутки?</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Какие форматы психологической помощи вам удобны?</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Вы хотели бы получить индивидуальную консультацию специалиста?</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Оставьте комментарий или пожелание к работе психологического центра</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="n">
+        <v>46149.0351975926</v>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>женский</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>иногда</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>учеба; общение</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>4</v>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>учеба, общение</t>
+        </is>
       </c>
       <c r="F2" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>прогулка, музыка, разговор с близкими</t>
-        </is>
+      <c r="G2" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
+          <t>Тикток</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>скорее нет</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>очная консультация, онлайн-консультация</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n">
+        <v>46149.10353021991</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>мужской</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>часто</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>учеба, работа, общение</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Хороший отдых</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
           <t>скорее да</t>
         </is>
       </c>
-      <c r="I2" s="2" t="n">
+      <c r="J3" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>очная консультация; письменные рекомендации</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>очная консультация</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
+        <v>46149.10394046296</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>женский</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>иногда</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>семья, здоровье</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Сон</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>групповая встреча</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>возможно</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>Хотелось бы больше информации о консультациях.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>мужской</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>часто</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>работа; здоровье</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="F3" s="2" t="n">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>46149.10712831018</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>предпочитаю не указывать</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>иногда</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>учеба</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>спорт и отдых без телефона</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="G5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Еда</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>скорее нет</t>
         </is>
       </c>
-      <c r="I3" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J5" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>онлайн-консультация</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>Удобно, если можно записаться онлайн.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>женский</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>редко</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>учеба</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>сон, чтение, прогулки</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>очная консультация; групповая встреча</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>Информация на сайте понятная.</t>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Нет</t>
         </is>
       </c>
     </row>
@@ -718,32 +817,174 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Показатель</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Значение</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Количество реальных ответов</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Период ответов</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>07.05.2026 00:50 - 07.05.2026 02:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Средний психологический комфорт</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Средняя легкость обращения за помощью</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Средняя продолжительность сна</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Пол</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>женский: 2; мужской: 1; предпочитаю не указывать: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Эмоциональное напряжение</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>иногда: 3; часто: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Источники стресса</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>учеба: 3; общение: 2; работа: 1; семья: 1; здоровье: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Удобные форматы помощи</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>очная консультация: 2; онлайн-консультация: 2; групповая встреча: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Готовность к индивидуальной консультации</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>да: 3; возможно: 1</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Вопрос</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Тип</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Пояснение</t>
         </is>
